--- a/data/seed/portfolio/L-2024-9958/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-9958/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,272 +535,277 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>6541000</v>
+        <v>954000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №9294 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата по счет-фактуре №6678 за поставленный товар</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>32541000</v>
+        <v>26954000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>1978000</v>
-      </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>897000</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Xiva Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>251735331</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000178228249001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №241/26</t>
+          <t>Оплата за продукцию по договору №244/26, НДС 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>30563000</v>
+        <v>27851000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>2630000</v>
+        <v>681000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Shartnoma №170/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8672 01.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>33193000</v>
+        <v>28532000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46208</v>
+        <v>46205</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>1335000</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9958)</t>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16307000315515899417</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9958 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №9294</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>23193000</v>
+        <v>29867000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>2610000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>546000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Shodlik Yog'och XK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>250789489</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000809211035001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №130/26, QQS bilan</t>
+          <t>Оплата за товар по с/ф №6559 от 03.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>20583000</v>
+        <v>30413000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>11053000</v>
+        <v>2381000</v>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Samarqand Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №28/26</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9530000</v>
+        <v>28032000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>12473000</v>
+        <v>10000000</v>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>257169749</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9958)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>16307000315515899417</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №187/26</t>
+          <t>Kredit shartnomasi L-2024-9958 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-2943000</v>
+        <v>18032000</v>
       </c>
     </row>
     <row r="15">
@@ -810,63 +815,63 @@
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>27852000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>2900000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zarafshon Qog'oz XK</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>354293161</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000881865117001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №49/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №262/26 т 06.07.2026</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-30795000</v>
+        <v>20932000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>1160000</v>
-      </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n">
+        <v>1790000</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Namangan Qurilish Materiallari AJ</t>
+          <t>Afrosiyob Agro MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>223523724</t>
+          <t>390124006</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000308383754001</t>
+          <t>20208000519249142001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -876,37 +881,37 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №94/24</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3435</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-31955000</v>
+        <v>22722000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>1783000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>1669000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -916,717 +921,712 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4073</t>
+          <t>Предоплата за товар по договору №143/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-33738000</v>
+        <v>24391000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>39328000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>493000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qo'qon Metall XK</t>
+          <t>Angren Qog'oz XK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>397010581</t>
+          <t>307544622</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000192306047001</t>
+          <t>20208000019851111001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №292/26</t>
+          <t>Оплата за товар по счет-фактуре №871 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-73066000</v>
+        <v>24884000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46213</v>
+        <v>46209</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>4995000</v>
-      </c>
+      <c r="C19" s="2" t="n">
+        <v>8736000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nihol Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>340579025</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000646910348001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №249/26, QQS 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №5287</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-68071000</v>
+        <v>16148000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
-        <v>1416000</v>
-      </c>
+      <c r="C20" s="2" t="n">
+        <v>9782000</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №267/26 от 13.07.2026</t>
+          <t>Оплата за сырье по дог. №104/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-66655000</v>
+        <v>6366000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46217</v>
+        <v>46209</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1507000</v>
+        <v>11053000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №8866</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-68162000</v>
+        <v>-4687000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46217</v>
+        <v>46210</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>1507000</v>
-      </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>1643000</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Оплата за товар по счет-фактуре №641 от 07.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-69669000</v>
+        <v>-3044000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46219</v>
+        <v>46211</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>1039000</v>
+        <v>1238000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Xiva Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>251735331</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000178228249001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №10/26, QQS 12%</t>
+          <t>Оплата за продукцию по дог. №95/26, НДС 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-68630000</v>
+        <v>-1806000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46223</v>
+        <v>46211</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>127417000</v>
+        <v>462000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nurafshon Mebel XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>274749159</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000217170198001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8533 за поставленный товар</t>
+          <t>Предоплата за товар по договору №268/26 от 08.07.2026</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>58787000</v>
+        <v>-1344000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46223</v>
+        <v>46211</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>3029000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>18558000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2101 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №87/26</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>61816000</v>
+        <v>-19902000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46223</v>
+        <v>46212</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>7164000</v>
+        <v>1160000</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Urganch Qurilish AJ</t>
+          <t>Kattaqo'rg'on Qurilish MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>258337226</t>
+          <t>252372463</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000780308650001</t>
+          <t>20208000838375427001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №90/26</t>
+          <t>Арендная плата за июль 2026 г. по дог. №40/25</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>54652000</v>
+        <v>-21062000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46224</v>
+        <v>46213</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>1326000</v>
+        <v>2540000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №31/26 от 21.07.2026</t>
+          <t>Оплата за продукцию по договору №133/26, НДС 12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>55978000</v>
+        <v>-18522000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46224</v>
+        <v>46213</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>1991000</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n">
+        <v>1020000</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>Оплата за продукцию по договору №249/26, НДС 12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>53987000</v>
+        <v>-17502000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46226</v>
+        <v>46213</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>3020000</v>
+        <v>814000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №150/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №2064 за поставленный товар</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>57007000</v>
+        <v>-16688000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46226</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>1773000</v>
+        <v>12209000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3530 23.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №155/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>58780000</v>
+        <v>-4479000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46226</v>
+        <v>46216</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>9941000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>3320000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Buxoro Meva Eksport MChJ</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>337405790</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000536469103001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №7219</t>
+          <t>Shartnoma №267/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>48839000</v>
+        <v>-1159000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46227</v>
+        <v>46216</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>2864000</v>
+        <v>1459000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jizzax Dori-Darmon MChJ</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>229827964</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000836118859001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №270/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5934</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>51703000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46230</v>
+        <v>46217</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>1352000</v>
+        <v>26771000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jizzax Dori-Darmon MChJ</t>
+          <t>Sharq Savdo MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>229827964</t>
+          <t>338611342</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000836118859001</t>
+          <t>20208000711708710001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Yetkazilga tovar uchun to'lov h/f №8749</t>
+          <t>Оплата за товар по счет-фактуре №8893 от 14.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>53055000</v>
+        <v>27071000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46230</v>
+        <v>46218</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>971000</v>
+        <v>1380000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Afrosiyob Agro MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>390124006</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000519249142001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №271/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №175 от 15.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>54026000</v>
+        <v>28451000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46230</v>
+        <v>46218</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>725000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>1019000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000759483534001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1636,352 +1636,357 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №46/26, НДС 12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>53301000</v>
+        <v>29470000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46231</v>
+        <v>46218</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>4134000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>1507000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №73/26 от 28.07.2026</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>57435000</v>
+        <v>27963000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46231</v>
+        <v>46218</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>1417000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>1507000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №139/26, QQS 12%</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>58852000</v>
+        <v>26456000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46231</v>
+        <v>46219</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>5930000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>1454000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Urganch Qurilish AJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>258337226</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000780308650001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9247</t>
+          <t>Оплата за продукцию по договору №10/26, НДС 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>52922000</v>
+        <v>27910000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46233</v>
+        <v>46219</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>2011000</v>
+        <v>1007000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Xiva Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>251735331</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000178228249001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №153/26 от 30.07.2026</t>
+          <t>Оплата по с/ф №8099 за поставленный товар</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>54933000</v>
+        <v>28917000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46234</v>
+        <v>46219</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>454000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Xiva Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>251735331</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000178228249001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за продукцию по договору №248/26, НДС 12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>54633000</v>
+        <v>29371000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46234</v>
+        <v>46219</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>31617000</v>
+        <v>1669000</v>
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Buxoro Meva Eksport MChJ</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>337405790</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000536469103001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №69/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №7025</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>23016000</v>
+        <v>27702000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46237</v>
+        <v>46220</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>10624000</v>
+        <v>2094000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Xiva Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>251735331</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000178228249001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Shartnoma №116/26 bo'icha oldindan to'lov</t>
+          <t>Shartnoma №67/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>33640000</v>
+        <v>29796000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>4632000</v>
+        <v>900000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №105/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2101 20.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>38272000</v>
+        <v>30696000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>1335000</v>
+        <v>688000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jizzax Dori-Darmon MChJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>229827964</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000836118859001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1991,77 +1996,77 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №98/26, QQS 12%</t>
+          <t>Оплата за продукцию по дог. №131/26, НДС 12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>39607000</v>
+        <v>31384000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>3103000</v>
+        <v>3636000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Qo'qon Metall XK</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>397010581</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000192306047001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №23/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №6561</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>36504000</v>
+        <v>27748000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46237</v>
+        <v>46224</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>3316000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>1587000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2071,117 +2076,117 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №84/26</t>
+          <t>Оплата за товар по с/ф №9089 от 21.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>33188000</v>
+        <v>29335000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46237</v>
+        <v>46225</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>12804000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>446000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Angren Qog'oz XK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>307544622</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000019851111001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2760</t>
+          <t>Оплата по счет-фактуре №5787 за поставленный товар</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>20384000</v>
+        <v>29781000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>2520000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>1896000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>315901240</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000665192491001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №51/26, QQS 12%</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>22904000</v>
+        <v>27885000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>16223000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>64689000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2191,347 +2196,357 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №3661</t>
+          <t>Оплата за продукцию по договору №150/26, НДС 12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>6681000</v>
+        <v>92574000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46239</v>
+        <v>46226</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>2117000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9958)</t>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>16307000315515899417</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9958 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за продукцию по дог. №246/26, НДС 12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>-3319000</v>
+        <v>94691000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46240</v>
+        <v>46226</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>2767000</v>
+        <v>1071000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Termiz Mato MChJ</t>
+          <t>Angren Qog'oz XK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>269386113</t>
+          <t>307544622</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000257117087001</t>
+          <t>20208000019851111001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №163/26, QQS 12%</t>
+          <t>Shartnoma №278/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>-552000</v>
+        <v>95762000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46240</v>
+        <v>46226</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>11112000</v>
+        <v>5435000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Samarqand Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>Оплата за транспортные услуги по договору №212/26</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>-11664000</v>
+        <v>90327000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46241</v>
+        <v>46227</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>1990000</v>
+        <v>2098000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Angren Qog'oz XK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>307544622</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000019851111001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №229/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №270/26, НДС 12%</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>-9674000</v>
+        <v>92425000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46241</v>
+        <v>46230</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>2698000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>4620000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Urganch Qurilish AJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>258337226</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000780308650001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4988</t>
+          <t>Оплата за товар по счет-фактуре №6155 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>-12372000</v>
+        <v>97045000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>5968000</v>
+        <v>718000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Angren Qog'oz XK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>307544622</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000019851111001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №250/26, НДС 12%</t>
+          <t>Оплата по счт-фактуре №8749 за поставленный товар</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>-6404000</v>
+        <v>97763000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>1166000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>686000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Namangan Qurilish Materiallari AJ</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>223523724</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000308383754001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov avgust</t>
+          <t>Оплата за продукцию по договору №271/26, НДС 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>-7570000</v>
+        <v>98449000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>3523000</v>
+        <v>725000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000948353491001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №202/26</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>-11093000</v>
+        <v>97724000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46244</v>
+        <v>46231</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>4286000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>1537000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2541,37 +2556,37 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №7/26</t>
+          <t>Оплата за продукцию по дог. №139/26, НДС 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>-15379000</v>
+        <v>99261000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46244</v>
+        <v>46231</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>6490000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>1533000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2581,277 +2596,272 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №99/26</t>
+          <t>Shartnoma №73/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>-21869000</v>
+        <v>100794000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46245</v>
+        <v>46231</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>2531000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>527000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Mehnat Logistik MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>342362872</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000205558906001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №25/26</t>
+          <t>Оплата за товар по с/ф №9454 от 28.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>-24400000</v>
+        <v>101321000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46247</v>
+        <v>46231</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>2904000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>3280000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nurafshon Mebel XK</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>274749159</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000217170198001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Shartnoma №197/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №2778</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>-21496000</v>
+        <v>98041000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46248</v>
+        <v>46232</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>4124000</v>
+        <v>2535000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3433</t>
+          <t>Оплата за товар по счет-фактуре №7932 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>-17372000</v>
+        <v>100576000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46248</v>
+        <v>46232</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>1515000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>552000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Angren Qog'oz XK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>307544622</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000019851111001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9206</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>-18887000</v>
+        <v>101128000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46248</v>
+        <v>46233</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>1515000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>801000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Оплата за товар по с/ф №2008 от 30.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>-20402000</v>
+        <v>101929000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46248</v>
+        <v>46233</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>10445000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>719000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Buxoro Meva Eksport MChJ</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>337405790</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000536469103001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6351</t>
+          <t>Shartnoma №153/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>-30847000</v>
+        <v>102648000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46251</v>
+        <v>46234</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n">
-        <v>1269000</v>
-      </c>
+      <c r="C66" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>317594417</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2861,437 +2871,432 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №155/26, QQS 12%</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>-29578000</v>
+        <v>102348000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46251</v>
+        <v>46234</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>2160000</v>
+        <v>79784000</v>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Sarbon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>382796418</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000611885904001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №55/26, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №5115</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>-31738000</v>
+        <v>22564000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>4260000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>12692000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Qo'qon Metall XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>397010581</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000192306047001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №98/26</t>
+          <t>Оплата за товар по счет-фактуре №1111 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>-35998000</v>
+        <v>35256000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46252</v>
+        <v>46237</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>6386000</v>
+        <v>5180000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7009</t>
+          <t>Оплата по счет-фактуре №5248 за поставленный товар</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>-29612000</v>
+        <v>40436000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46252</v>
+        <v>46237</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>5190000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>5108000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Qo'qon Metall XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>397010581</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000192306047001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3371</t>
+          <t>Оплата по счет-фактуре №5971 за поставленный товар</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>-34802000</v>
+        <v>45544000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46255</v>
+        <v>46237</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n">
-        <v>80548000</v>
-      </c>
+      <c r="C71" s="2" t="n">
+        <v>11124000</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Sarbon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>382796418</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000611885904001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3367</t>
+          <t>Tovarlar uchun to'lov h/f №266</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>45746000</v>
+        <v>34420000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46255</v>
+        <v>46237</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>2145000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>34132000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Shartnoma №285/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №83/26</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>47891000</v>
+        <v>288000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46255</v>
+        <v>46238</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>5522000</v>
-      </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n">
+        <v>12841000</v>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Buxoro Non AJ</t>
+          <t>Mehnat Logistik MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>360293566</t>
+          <t>342362872</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000846253861001</t>
+          <t>20208000205558906001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №69/26</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №16/26 ОТ 04.08.2026</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>42369000</v>
+        <v>13129000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46258</v>
+        <v>46239</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>5845000</v>
+        <v>2396000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1484</t>
+          <t>Оплата по счет-фактуре №2543 за поставленный товар</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>48214000</v>
+        <v>15525000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46258</v>
+        <v>46239</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>3497000</v>
+        <v>2039000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bog'ishamol Farm Savdo MChJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>371507894</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000978092110001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8423 24.08.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №1885 за поставленный товар</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>51711000</v>
+        <v>17564000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46258</v>
+        <v>46239</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>2444000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>4641000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Oziq-ovqat Savdo AJ</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>344517353</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000111782282001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6888 24.08.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №239/26</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>54155000</v>
+        <v>12923000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46258</v>
+        <v>46239</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>1593000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>317594417</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9958)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>16307000315515899417</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3301,157 +3306,152 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5048</t>
+          <t>Kredit shartnomasi L-2024-9958 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>55748000</v>
+        <v>2923000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46258</v>
+        <v>46239</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>729000</v>
+        <v>11112000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>200933985</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000759483534001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>ISH HAQI TO'LOVI IYUL 2026 (PLASTIK KARTALARGA)</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>55019000</v>
+        <v>-8189000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46258</v>
+        <v>46241</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>1954000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>5864000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Оплата за продукцию по договору №180/26, НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>53065000</v>
+        <v>-2325000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46258</v>
+        <v>46241</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>2920000</v>
+        <v>3456000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №237/26</t>
+          <t>Оплата за сырье по договору №13/26 от 07.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>50145000</v>
+        <v>-5781000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46259</v>
+        <v>46244</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>7206000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>14320000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3461,77 +3461,77 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3984</t>
+          <t>Оплата по счет-фактуре №7924 за поставленный товар</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>42939000</v>
+        <v>8539000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46260</v>
+        <v>46244</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>8327000</v>
+        <v>4080000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Olmaliq Savdo XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>274915992</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000717019874001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №260 26.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №1395 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>51266000</v>
+        <v>12619000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46260</v>
+        <v>46244</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>21637000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>3089000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Urganch Qurilish AJ</t>
+          <t>Sharq Savdo MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>258337226</t>
+          <t>338611342</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000780308650001</t>
+          <t>20208000711708710001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3541,272 +3541,277 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4353</t>
+          <t>Оплата за продукцию по договору №164/26, НДС 12%</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>29629000</v>
+        <v>15708000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>3272000</v>
+        <v>2824000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Shartnoma №34/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №71/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>32901000</v>
+        <v>18532000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>4381000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>2250000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Urganch Qurilish AJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>258337226</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000780308650001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №117/26</t>
+          <t>Оплата за товар по с/ф №7155 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>28520000</v>
+        <v>20782000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>3693000</v>
+        <v>2041000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Xiva Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>251735331</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000178228249001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Shartnoma №250/26 boyicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №23/26, QQS 12%</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>32213000</v>
+        <v>22823000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>3602000</v>
+        <v>1304000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6528</t>
+          <t>Оплата за товар по счет-фактуре №2179 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>35815000</v>
+        <v>24127000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>3380000</v>
+        <v>1249000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nurafshon Mebel XK</t>
+          <t>Sharq Savdo MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>274749159</t>
+          <t>338611342</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000217170198001</t>
+          <t>20208000711708710001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №495 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №175/26, НДС 12%</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>39195000</v>
+        <v>25376000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>1183000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Tovar uchun to'lov, h/f №9265 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>38895000</v>
+        <v>26559000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>5752000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>1126000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3816,37 +3821,37 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №151/26</t>
+          <t>Оплата за товар по с/ф №2031 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>33143000</v>
+        <v>27685000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>6194000</v>
+        <v>1166000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Buxoro Non AJ</t>
+          <t>Kattaqo'rg'on Qurilish MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>360293566</t>
+          <t>252372463</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000846253861001</t>
+          <t>20208000838375427001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3856,157 +3861,157 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №203/26, QQS bilan</t>
+          <t>Аренда помещения за август, дог. №40/25</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>26949000</v>
+        <v>26519000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46265</v>
+        <v>46245</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>6208000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>4866000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Buxoro Non AJ</t>
+          <t>Shodlik Yog'och XK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>360293566</t>
+          <t>250789489</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000846253861001</t>
+          <t>20208000809211035001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3979</t>
+          <t>Оплата за продукцию по договору №282/26, НДС 12%</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>20741000</v>
+        <v>31385000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46266</v>
+        <v>46245</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>4231000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>18569000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Oziq-ovqat Savdo AJ</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>344517353</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000111782282001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1836</t>
+          <t>Оплата за сырье по дог. №267/26 от 11.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>24972000</v>
+        <v>12816000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46266</v>
+        <v>46246</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>3881000</v>
-      </c>
+      <c r="C94" s="2" t="n">
+        <v>5599000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №66/26 ОТ 01.09.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №3293</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>28853000</v>
+        <v>7217000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46267</v>
+        <v>46247</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>6897000</v>
+        <v>1936000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Jizzax Dori-Darmon MChJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>229827964</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000836118859001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4016,117 +4021,117 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №13/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №5601 от 13.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>35750000</v>
+        <v>9153000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46267</v>
+        <v>46248</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>3547000</v>
+        <v>1037000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №383</t>
+          <t>Оплата по с/ф №3236 за поставленный товар</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>39297000</v>
+        <v>10190000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46267</v>
+        <v>46248</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>1626000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>7602000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5248</t>
+          <t>Оплата за сырье по договору №139/26 от 14.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>40923000</v>
+        <v>2588000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46267</v>
+        <v>46251</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>4710000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>4451000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4136,37 +4141,37 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4696</t>
+          <t>Оплата за товар по счет-фактуре №7640 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>36213000</v>
+        <v>7039000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46267</v>
+        <v>46251</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>6775000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>3156000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4176,907 +4181,917 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №162/26</t>
+          <t>Оплата за товар по с/ф №5710 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>29438000</v>
+        <v>10195000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46268</v>
+        <v>46251</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>8594000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>2281000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5054</t>
+          <t>Оплата по счет-фактуре №2818 за поставленный товар</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>20844000</v>
+        <v>12476000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46270</v>
+        <v>46251</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>1273000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9958)</t>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>16307000315515899417</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9958 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Предоплата за товар по договору №95/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>10844000</v>
+        <v>13749000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46272</v>
+        <v>46251</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>6948000</v>
+        <v>971000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Xiva Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>251735331</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000178228249001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7155 07.09.2026, QQS bilan</t>
+          <t>Shartnoma №119/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>17792000</v>
+        <v>14720000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46272</v>
+        <v>46251</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>1763000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>1515000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2543</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>19555000</v>
+        <v>13205000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46272</v>
+        <v>46251</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>1593000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>1515000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Shartnoma №129/26 bo'yicha oldindan to'lov</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>21148000</v>
+        <v>11690000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46272</v>
+        <v>46251</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>12297000</v>
+        <v>3735000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Samarqand Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №7046</t>
+          <t>Оплата за транспортные услуги по дог. №175/26</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>8851000</v>
+        <v>7955000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46273</v>
+        <v>46252</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>4680000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>10621000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nurafshon Mebel XK</t>
+          <t>Namangan Plastik MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>274749159</t>
+          <t>236741347</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000217170198001</t>
+          <t>20208000801934777001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1395 08.09.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №5428</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>13531000</v>
+        <v>-2666000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46273</v>
+        <v>46254</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>2919000</v>
+        <v>1552000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Termiz Mato MChJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>269386113</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000257117087001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №175/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №246/26 от 20.08.2026</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>16450000</v>
+        <v>-1114000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46273</v>
+        <v>46254</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>1861000</v>
+        <v>1346000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nurafshon Mebel XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>274749159</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000217170198001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №227/26, QQS 12%</t>
+          <t>Оплата за продукцию по дог. №183/26, НДС 12%</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>18311000</v>
+        <v>232000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46273</v>
+        <v>46254</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>1324000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Namangan Qurilish Materiallari AJ</t>
+          <t>Angren Qog'oz XK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>223523724</t>
+          <t>307544622</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000308383754001</t>
+          <t>20208000019851111001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №94/24</t>
+          <t>Оплата за продукцию по договору №100/26, НДС 12%</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>17021000</v>
+        <v>1556000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46274</v>
+        <v>46254</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>1845000</v>
+        <v>954000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Termiz Mato MChJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>269386113</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000257117087001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №164/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №138/26, НДС 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>18866000</v>
+        <v>2510000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46274</v>
+        <v>46255</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>3267000</v>
+        <v>1876000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Buxoro Non AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>360293566</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000846253861001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №30/26, QQS bilan</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>15599000</v>
+        <v>634000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46275</v>
+        <v>46255</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>1556000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>1942000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №249/26, QQS 12%</t>
+          <t>Оплата за сырье по договору №270/26 от 21.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>17155000</v>
+        <v>-1308000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46275</v>
+        <v>46255</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>9152000</v>
+        <v>7436000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №37/26</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №165/26 ОТ 21.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>8003000</v>
+        <v>-8744000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46276</v>
+        <v>46258</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>3937000</v>
+        <v>5075000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №324 11.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №47/26 от 24.08.2026</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>11940000</v>
+        <v>-3669000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46276</v>
+        <v>46258</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>16914000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>2524000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Mehnat Logistik MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>342362872</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000205558906001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №220/26</t>
+          <t>Оплата по счет-фактуре №1843 за поставленный товар</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>-4974000</v>
+        <v>-1145000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46279</v>
+        <v>46258</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n">
-        <v>10043000</v>
-      </c>
+      <c r="C116" s="2" t="n">
+        <v>2317000</v>
+      </c>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №159/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №7903</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>5069000</v>
+        <v>-3462000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46279</v>
+        <v>46258</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>1462000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>7515000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nihol Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>340579025</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000646910348001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5971</t>
+          <t>Tovarlar uchun to'lov h/f 5225</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>6531000</v>
+        <v>-10977000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46279</v>
+        <v>46259</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>1310000</v>
+        <v>6051000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3236</t>
+          <t>Оплата по счет-фактуре №4474 за поставленный товар</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>7841000</v>
+        <v>-4926000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46279</v>
+        <v>46259</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>1677000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>5734000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq avgust 2026</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №9929</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>6164000</v>
+        <v>808000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46279</v>
+        <v>46259</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>1677000</v>
+        <v>729000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000948353491001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>4487000</v>
+        <v>79000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46279</v>
+        <v>46260</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>3166000</v>
+        <v>1984000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Sarbon Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>382796418</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000611885904001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №133/26, QQS bilan</t>
+          <t>Оплата за сырье по договору №291/26 от 26.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1321000</v>
+        <v>-1905000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46279</v>
+        <v>46260</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>10641000</v>
+        <v>5299000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Urganch Qurilish AJ</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>258337226</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000780308650001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5086,357 +5101,352 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №283/26</t>
+          <t>Оплата за транспортные услуги по договору №209/26</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>-9320000</v>
+        <v>-7204000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46279</v>
+        <v>46261</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>26730000</v>
+        <v>3663000</v>
       </c>
       <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Samarqand Qurilish MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>334122225</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000530359436001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №204/26</t>
+          <t>Оплата за товары согласно счет-фактуре №8733</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>-36050000</v>
+        <v>-10867000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46281</v>
+        <v>46262</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>3890000</v>
+        <v>15216000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2818</t>
+          <t>Предоплата за товар по дог. №135/26 от 28.08.2026</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>-32160000</v>
+        <v>4349000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>1624000</v>
+        <v>2440000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №562 за поставленный товар</t>
+          <t>Предоплата за товар по договору №213/26 от 28.08.2026</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>-30536000</v>
+        <v>6789000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46286</v>
+        <v>46262</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>28872000</v>
+        <v>1207000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Xiva Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>251735331</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000178228249001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №157/26, НДС 12%</t>
+          <t>Оплата п счет-фактуре №1784 за поставленный товар</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>-1664000</v>
+        <v>7996000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>7370000</v>
+        <v>5334000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Shartnoma №246/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №197/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>5706000</v>
+        <v>13330000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>5861000</v>
+        <v>3873000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №9178 ОТ 21.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №85/26 от 31.08.2026</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>11567000</v>
+        <v>17203000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>5836000</v>
+        <v>2393000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2165 21.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №258/26 от 31.08.2026</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>17403000</v>
+        <v>19596000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>2858000</v>
+        <v>1747000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Namangan Plastik MChJ</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>224367413</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000768019347001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2420 21.09.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4961 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>20261000</v>
+        <v>21343000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>1864000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>317594417</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5446,317 +5456,312 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Shartnoma №253/26 bo'yicha oldindan to'lov</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>22125000</v>
+        <v>21043000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46286</v>
+        <v>46267</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>1812000</v>
+        <v>3592000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №260/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №310 за поставленный товар</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>23937000</v>
+        <v>24635000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46286</v>
+        <v>46267</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>1462000</v>
+        <v>752000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>240860816</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9616 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №8430 за поставленный товар</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>25399000</v>
+        <v>25387000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46286</v>
+        <v>46268</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>2219000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>8797000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за август</t>
+          <t>ОПЛАТА ПО С/Ф №3252 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>23180000</v>
+        <v>34184000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46287</v>
+        <v>46268</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>8297000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>2025000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Buxoro Non AJ</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>360293566</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000846253861001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №258/26</t>
+          <t>Оплата за продукцию по дог. №4/26, НДС 12%</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>14883000</v>
+        <v>36209000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46288</v>
+        <v>46268</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>2237000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>21971000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Oziq-ovqat Savdo AJ</t>
+          <t>Namangan Plastik MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>344517353</t>
+          <t>236741347</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000111782282001</t>
+          <t>20208000801934777001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №268/26, QQS 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №7634</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>17120000</v>
+        <v>14238000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46288</v>
+        <v>46269</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>1295000</v>
+        <v>18092000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Shartnoma №47/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №187/26 от 04.09.2026</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>18415000</v>
+        <v>32330000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46288</v>
+        <v>46269</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>806000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>4352000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000759483534001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>Оплата по счет-фактуре №2930 за поставленный товар</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>17609000</v>
+        <v>36682000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46289</v>
+        <v>46269</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>7661000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>12297000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>317594417</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5766,37 +5771,32 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №9929 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>25270000</v>
+        <v>24385000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46290</v>
+        <v>46270</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>1090000</v>
-      </c>
+      <c r="C140" s="2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bunyodkor Tikuv MChJ</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>240860816</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9958)</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000062919531001</t>
+          <t>16307000315515899417</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5806,391 +5806,2071 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №114/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2024-9958 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>26360000</v>
+        <v>14385000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46293</v>
+        <v>46272</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>1705000</v>
+        <v>6453000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Shartnoma №135/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №11/26, QQS 12%</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>28065000</v>
+        <v>20838000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46293</v>
+        <v>46272</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>1667000</v>
+        <v>5934000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №197/26 от 28.09.2026</t>
+          <t>Предоплата за товар по договору №129/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>29732000</v>
+        <v>26772000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46293</v>
+        <v>46272</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>1128000</v>
+        <v>4959000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Oziq-ovqat Savdo AJ</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>344517353</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000111782282001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f 7900 28.09.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №5534 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>30860000</v>
+        <v>31731000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46293</v>
+        <v>46272</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>1084000</v>
+        <v>3655000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Xiva Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>251735331</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000178228249001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7312</t>
+          <t>Оплата по счет-фактуре №3321 за поставленный товар</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>31944000</v>
+        <v>35386000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46293</v>
+        <v>46272</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>8455000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>2593000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Angren Qog'oz XK</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>307544622</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000019851111001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2502</t>
+          <t>Оплата за товар по счет-фактуре №3538 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>23489000</v>
+        <v>37979000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46293</v>
+        <v>46272</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n">
-        <v>17570000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n">
+        <v>2131000</v>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Qo'qon Metall XK</t>
+          <t>Sarbon Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>397010581</t>
+          <t>286081690</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000192306047001</t>
+          <t>20208000291953120001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №209/26</t>
+          <t>Оплата за продукцию по дог. №266/26, НДС 12%</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>5919000</v>
+        <v>40110000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46294</v>
+        <v>46272</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>45479000</v>
+        <v>1744000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Nukus Qurilish Materiallari XK</t>
+          <t>Nukus Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>317594417</t>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000113475423001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Shartnoma №258/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №7055 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>51398000</v>
+        <v>41854000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46295</v>
+        <v>46272</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
-      <c r="C148" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>1366000</v>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>359441781</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000347542301001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Предоплата за товар по договору №122/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>51098000</v>
+        <v>43220000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46295</v>
+        <v>46272</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>26598000</v>
+        <v>1290000</v>
       </c>
       <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Tong Tikuv XK</t>
+          <t>Kattaqo'rg'on Qurilish MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>257169749</t>
+          <t>252372463</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000088150643001</t>
+          <t>20208000838375427001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Аренда помещения за сентябрь, дог. №40/25</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>41930000</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B150" t="n">
+        <v>242</v>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>4159000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Samarqand Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>334122225</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>20208000530359436001</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №230/26</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>37771000</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B151" t="n">
+        <v>243</v>
+      </c>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>6268000</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>359441781</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>20208000347542301001</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
           <t>01153</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №115/26</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="n">
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №4527 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>44039000</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B152" t="n">
+        <v>244</v>
+      </c>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n">
+        <v>2915000</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Angren Qog'oz XK</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>307544622</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20208000019851111001</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №6892 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>46954000</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B153" t="n">
+        <v>245</v>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>5509000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Nihol Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>340579025</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>20208000646910348001</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №4548</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>41445000</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B154" t="n">
+        <v>246</v>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>1591000</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Sarbon Agro Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>286081690</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20208000291953120001</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3170</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>43036000</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B155" t="n">
+        <v>247</v>
+      </c>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n">
+        <v>8348000</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>359441781</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20208000347542301001</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №260/26 от 14.09.2026</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>51384000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B156" t="n">
+        <v>248</v>
+      </c>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>3043000</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Sarbon Agro Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>286081690</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000291953120001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7025</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>54427000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B157" t="n">
+        <v>249</v>
+      </c>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>1582000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>359441781</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000347542301001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №23/26 от 14.09.2026</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>56009000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B158" t="n">
+        <v>250</v>
+      </c>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>1114000</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Sarbon Agro Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>286081690</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000291953120001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №97/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>57123000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B159" t="n">
+        <v>251</v>
+      </c>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>699000</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Olmaliq Savdo XK</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>274915992</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000717019874001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Shartnoma №200/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>57822000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B160" t="n">
+        <v>252</v>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>1677000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Социальный налог за август 2026 г.</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>56145000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B161" t="n">
+        <v>253</v>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>1677000</v>
+      </c>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>JShDS avgust oyi uchun</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>54468000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B162" t="n">
+        <v>254</v>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>5185000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Samarqand Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>334122225</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000530359436001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по договору №95/26 от 15.09.2026, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>49283000</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>18009000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Xiva Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>229356608</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000625386165001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun tolov, shartnoma №6/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>31274000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B164" t="n">
+        <v>256</v>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>7851000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Xiva Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>251735331</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000178228249001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №1655 от 16.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>39125000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B165" t="n">
+        <v>257</v>
+      </c>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>1142000</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Angren Qog'oz XK</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>307544622</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000019851111001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №3152 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>40267000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B166" t="n">
+        <v>258</v>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>17200000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Navoiy Trans Servis AJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>301058191</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000230604750001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №213/26</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>23067000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B167" t="n">
+        <v>259</v>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Xiva Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>229356608</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000625386165001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartn. №37/26</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>5567000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B168" t="n">
+        <v>260</v>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>3078000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Xiva Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>251735331</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000178228249001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №271/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>8645000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B169" t="n">
+        <v>261</v>
+      </c>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n">
+        <v>1923000</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>359441781</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000347542301001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-факуре №374 от 18.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>10568000</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B170" t="n">
+        <v>262</v>
+      </c>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n">
+        <v>862000</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>359441781</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000347542301001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №3956 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>11430000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B171" t="n">
+        <v>263</v>
+      </c>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n">
+        <v>20148000</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Sarbon Agro Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>286081690</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000291953120001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №75/26 от 21.09.2026</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>31578000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B172" t="n">
+        <v>264</v>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>8673000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>359441781</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000347542301001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №8125 21.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>40251000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B173" t="n">
+        <v>265</v>
+      </c>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n">
+        <v>5243000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>359441781</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000347542301001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №5241 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>45494000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B174" t="n">
+        <v>266</v>
+      </c>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n">
+        <v>4970000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Sarbon Agro Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>286081690</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000291953120001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №541 от 21.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>50464000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B175" t="n">
+        <v>267</v>
+      </c>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n">
+        <v>1464000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>359441781</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000347542301001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №9112 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>51928000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B176" t="n">
+        <v>268</v>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>6491000</v>
+      </c>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Xiva Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>229356608</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20208000625386165001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №197/26 ОТ 21.09.2026, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>45437000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B177" t="n">
+        <v>269</v>
+      </c>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n">
+        <v>9544000</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Sarbon Agro Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>286081690</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20208000291953120001</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №8817 от 22.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>54981000</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B178" t="n">
+        <v>270</v>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>2118000</v>
+      </c>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Уплата налога на добавленную стоимость за август</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>52863000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B179" t="n">
+        <v>271</v>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>806000</v>
+      </c>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>20208000948353491001</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию согласно счету</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>52057000</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B180" t="n">
+        <v>272</v>
+      </c>
+      <c r="C180" s="2" t="n">
+        <v>14253000</v>
+      </c>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Namangan Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>236741347</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20208000801934777001</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №48/26</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>37804000</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B181" t="n">
+        <v>273</v>
+      </c>
+      <c r="C181" s="2" t="n">
+        <v>15829000</v>
+      </c>
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Samarqand Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>334122225</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>20208000530359436001</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №99/26</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>21975000</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B182" t="n">
+        <v>274</v>
+      </c>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n">
+        <v>3670000</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>359441781</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>20208000347542301001</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №188/26 от 24.09.2026</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>25645000</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B183" t="n">
+        <v>275</v>
+      </c>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n">
+        <v>877000</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Afrosiyob Agro MChJ</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>390124006</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>20208000519249142001</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №6056 от 25.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>26522000</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B184" t="n">
+        <v>276</v>
+      </c>
+      <c r="C184" s="2" t="n">
+        <v>16809000</v>
+      </c>
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Namangan Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>236741347</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>20208000801934777001</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по дог. №170/26 от 25.09.2026, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>9713000</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B185" t="n">
+        <v>277</v>
+      </c>
+      <c r="C185" s="2" t="n"/>
+      <c r="D185" s="2" t="n">
+        <v>3964000</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>359441781</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>20208000347542301001</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №2616 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>13677000</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B186" t="n">
+        <v>278</v>
+      </c>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n">
+        <v>1422000</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>359441781</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>20208000347542301001</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №73/26 от 28.09.2026</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>15099000</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B187" t="n">
+        <v>279</v>
+      </c>
+      <c r="C187" s="2" t="n"/>
+      <c r="D187" s="2" t="n">
+        <v>6491000</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Nukus Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>359441781</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>20208000347542301001</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №202/26 от 29.09.2026</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>21590000</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B188" t="n">
+        <v>280</v>
+      </c>
+      <c r="C188" s="2" t="n"/>
+      <c r="D188" s="2" t="n">
+        <v>1049000</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Sarbon Agro Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>286081690</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>20208000291953120001</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №8717 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v>22639000</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B189" t="n">
+        <v>281</v>
+      </c>
+      <c r="C189" s="2" t="n"/>
+      <c r="D189" s="2" t="n">
+        <v>1280000</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Angren Qog'oz XK</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>307544622</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>20208000019851111001</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №8025 от 30.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>23919000</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B190" t="n">
+        <v>282</v>
+      </c>
+      <c r="C190" s="2" t="n"/>
+      <c r="D190" s="2" t="n">
+        <v>881000</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Olmaliq Savdo XK</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>274915992</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>20208000717019874001</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №64/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>24800000</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B191" t="n">
+        <v>283</v>
+      </c>
+      <c r="C191" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Sarbon Moliya Bank</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="n">
         <v>24500000</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+    <row r="192">
+      <c r="A192" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C150" s="4" t="n">
-        <v>515194000</v>
-      </c>
-      <c r="D150" s="4" t="n">
-        <v>513694000</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="C192" s="4" t="n">
+        <v>492337000</v>
+      </c>
+      <c r="D192" s="4" t="n">
+        <v>490837000</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C151" s="4" t="n">
+      <c r="C193" s="4" t="n">
         <v>24500000</v>
       </c>
-      <c r="D151" s="4" t="n"/>
+      <c r="D193" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
